--- a/dirasakan.xlsx
+++ b/dirasakan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B099FA-8D64-4192-932A-2152680991A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F300D5-C3CC-45EA-9DAB-C4A01FF29183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="7500" windowHeight="9456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Tanggal</t>
   </si>
@@ -49,21 +49,14 @@
   </si>
   <si>
     <t>Dirasakan</t>
-  </si>
-  <si>
-    <t>22 km Tenggara Karangasem-Bali</t>
-  </si>
-  <si>
-    <t>dirasakan di wilayah Kab. Karangasem III MMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -91,17 +84,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -455,32 +443,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0.85359953703703706</v>
-      </c>
-      <c r="C2">
-        <v>-8.49</v>
-      </c>
-      <c r="D2">
-        <v>115.66</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>

--- a/dirasakan.xlsx
+++ b/dirasakan.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seismioto\Pengolahan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F300D5-C3CC-45EA-9DAB-C4A01FF29183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8059138-53C4-4FC3-BA7D-5D5AEB720E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="7500" windowHeight="9456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -55,12 +61,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -84,12 +100,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,16 +431,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822B08B2-1387-4C99-A9BB-7378259DE79F}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="159" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -443,8 +470,41 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3"/>
+      <c r="B2" s="7"/>
+      <c r="G2"/>
+      <c r="H2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3"/>
+      <c r="B3" s="7"/>
+      <c r="G3"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>